--- a/Function 4/evals.xlsx
+++ b/Function 4/evals.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prithvi\Desktop\Imperial Course\Capstone-Project\Function 4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7336C109-559F-4FF9-A6D4-0E8D26827D55}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98E87C0F-F889-405F-A789-89F864A8238B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -89,13 +89,13 @@
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -382,242 +382,261 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="2" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4" t="s">
+      <c r="C2" s="2"/>
+      <c r="D2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4" t="s">
+      <c r="E2" s="2"/>
+      <c r="F2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4" t="s">
+      <c r="G2" s="2"/>
+      <c r="H2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4" t="s">
+      <c r="I2" s="2"/>
+      <c r="J2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4" t="s">
+      <c r="K2" s="2"/>
+      <c r="L2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M2" s="2"/>
+      <c r="M2" s="3"/>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B3" s="2">
+      <c r="B3" s="3">
         <v>1</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2">
+      <c r="C3" s="3"/>
+      <c r="D3" s="3">
         <v>0</v>
       </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2">
+      <c r="E3" s="3"/>
+      <c r="F3" s="3">
         <v>0</v>
       </c>
-      <c r="G3" s="2"/>
-      <c r="H3" s="3">
+      <c r="G3" s="3"/>
+      <c r="H3" s="4">
         <v>1</v>
       </c>
-      <c r="I3" s="3"/>
-      <c r="J3" s="2">
+      <c r="I3" s="4"/>
+      <c r="J3" s="3">
         <v>1</v>
       </c>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2">
+      <c r="K3" s="3"/>
+      <c r="L3" s="3">
         <v>-40.348489596712497</v>
       </c>
-      <c r="M3" s="2"/>
+      <c r="M3" s="3"/>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B4" s="2">
+      <c r="B4" s="3">
         <v>2</v>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2">
+      <c r="C4" s="3"/>
+      <c r="D4" s="3">
         <v>0.38188439101149502</v>
       </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2">
+      <c r="E4" s="3"/>
+      <c r="F4" s="3">
         <v>0.40048806048405</v>
       </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2">
+      <c r="G4" s="3"/>
+      <c r="H4" s="3">
         <v>0.37367797637949901</v>
       </c>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2">
+      <c r="I4" s="3"/>
+      <c r="J4" s="3">
         <v>0.468096950835934</v>
       </c>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3">
+        <v>-1.20567449112958</v>
+      </c>
+      <c r="M4" s="3"/>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
+      <c r="B5" s="3">
+        <v>3</v>
+      </c>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3">
+        <v>0.47217455396691399</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3">
+        <v>0.45735404032243598</v>
+      </c>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3">
+        <v>0.21534414919209699</v>
+      </c>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3">
+        <v>0.422766391601334</v>
+      </c>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="3"/>
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="3"/>
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
     </row>
     <row r="9" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
     </row>
     <row r="11" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
     </row>
     <row r="12" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
     </row>
     <row r="13" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
     </row>
     <row r="14" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="58">
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="H4:I4"/>
+  <mergeCells count="62">
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="L5:M5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="L6:M6"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
     <mergeCell ref="D14:E14"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="D4:E4"/>
@@ -630,33 +649,30 @@
     <mergeCell ref="D11:E11"/>
     <mergeCell ref="D12:E12"/>
     <mergeCell ref="D13:E13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="H4:I4"/>
     <mergeCell ref="H5:I5"/>
     <mergeCell ref="H6:I6"/>
     <mergeCell ref="H7:I7"/>
     <mergeCell ref="H8:I8"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="J4:K4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Function 4/evals.xlsx
+++ b/Function 4/evals.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prithvi\Desktop\Imperial Course\Capstone-Project\Function 4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98E87C0F-F889-405F-A789-89F864A8238B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DDE2ECC-F91C-4381-A419-176B2EDC93A7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -408,10 +408,10 @@
       <c r="M2" s="3"/>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B3" s="3">
+      <c r="B3" s="2">
         <v>1</v>
       </c>
-      <c r="C3" s="3"/>
+      <c r="C3" s="2"/>
       <c r="D3" s="3">
         <v>0</v>
       </c>
@@ -434,10 +434,10 @@
       <c r="M3" s="3"/>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B4" s="3">
+      <c r="B4" s="2">
         <v>2</v>
       </c>
-      <c r="C4" s="3"/>
+      <c r="C4" s="2"/>
       <c r="D4" s="3">
         <v>0.38188439101149502</v>
       </c>
@@ -460,10 +460,10 @@
       <c r="M4" s="3"/>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B5" s="3">
+      <c r="B5" s="2">
         <v>3</v>
       </c>
-      <c r="C5" s="3"/>
+      <c r="C5" s="2"/>
       <c r="D5" s="3">
         <v>0.47217455396691399</v>
       </c>
@@ -480,19 +480,31 @@
         <v>0.422766391601334</v>
       </c>
       <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
+      <c r="L5" s="3">
+        <v>-3.7543251842156602</v>
+      </c>
       <c r="M5" s="3"/>
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
+      <c r="B6" s="2">
+        <v>4</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="3">
+        <v>0.47217500000000001</v>
+      </c>
       <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
+      <c r="F6" s="3">
+        <v>0.481364478139513</v>
+      </c>
       <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
+      <c r="H6" s="3">
+        <v>0.45430953159790799</v>
+      </c>
       <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
+      <c r="J6" s="3">
+        <v>0.40603051021903602</v>
+      </c>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>

--- a/Function 4/evals.xlsx
+++ b/Function 4/evals.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prithvi\Desktop\Imperial Course\Capstone-Project\Function 4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DDE2ECC-F91C-4381-A419-176B2EDC93A7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A2BA1FA-5DB4-4B5A-8AAC-2B3C5F6AE17A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -89,10 +89,10 @@
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -382,240 +382,240 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="2" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2" t="s">
+      <c r="C2" s="3"/>
+      <c r="D2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2" t="s">
+      <c r="E2" s="3"/>
+      <c r="F2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2" t="s">
+      <c r="G2" s="3"/>
+      <c r="H2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2" t="s">
+      <c r="I2" s="3"/>
+      <c r="J2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2" t="s">
+      <c r="K2" s="3"/>
+      <c r="L2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M2" s="3"/>
+      <c r="M2" s="2"/>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B3" s="2">
+      <c r="B3" s="3">
         <v>1</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="3">
+      <c r="C3" s="3"/>
+      <c r="D3" s="2">
         <v>0</v>
       </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3">
+      <c r="E3" s="2"/>
+      <c r="F3" s="2">
         <v>0</v>
       </c>
-      <c r="G3" s="3"/>
+      <c r="G3" s="2"/>
       <c r="H3" s="4">
         <v>1</v>
       </c>
       <c r="I3" s="4"/>
-      <c r="J3" s="3">
+      <c r="J3" s="2">
         <v>1</v>
       </c>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3">
+      <c r="K3" s="2"/>
+      <c r="L3" s="2">
         <v>-40.348489596712497</v>
       </c>
-      <c r="M3" s="3"/>
+      <c r="M3" s="2"/>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B4" s="2">
+      <c r="B4" s="3">
         <v>2</v>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="3">
+      <c r="C4" s="3"/>
+      <c r="D4" s="2">
         <v>0.38188439101149502</v>
       </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3">
+      <c r="E4" s="2"/>
+      <c r="F4" s="2">
         <v>0.40048806048405</v>
       </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3">
+      <c r="G4" s="2"/>
+      <c r="H4" s="2">
         <v>0.37367797637949901</v>
       </c>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3">
+      <c r="I4" s="2"/>
+      <c r="J4" s="2">
         <v>0.468096950835934</v>
       </c>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3">
+      <c r="K4" s="2"/>
+      <c r="L4" s="2">
         <v>-1.20567449112958</v>
       </c>
-      <c r="M4" s="3"/>
+      <c r="M4" s="2"/>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B5" s="2">
+      <c r="B5" s="3">
         <v>3</v>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="3">
+      <c r="C5" s="3"/>
+      <c r="D5" s="2">
         <v>0.47217455396691399</v>
       </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3">
+      <c r="E5" s="2"/>
+      <c r="F5" s="2">
         <v>0.45735404032243598</v>
       </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3">
+      <c r="G5" s="2"/>
+      <c r="H5" s="2">
         <v>0.21534414919209699</v>
       </c>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3">
+      <c r="I5" s="2"/>
+      <c r="J5" s="2">
         <v>0.422766391601334</v>
       </c>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3">
+      <c r="K5" s="2"/>
+      <c r="L5" s="2">
         <v>-3.7543251842156602</v>
       </c>
-      <c r="M5" s="3"/>
+      <c r="M5" s="2"/>
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B6" s="2">
+      <c r="B6" s="3">
         <v>4</v>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="3">
-        <v>0.47217500000000001</v>
-      </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3">
+      <c r="C6" s="3"/>
+      <c r="D6" s="2">
+        <v>0.41113387811130298</v>
+      </c>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2">
         <v>0.481364478139513</v>
       </c>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3">
+      <c r="G6" s="2"/>
+      <c r="H6" s="2">
         <v>0.45430953159790799</v>
       </c>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3">
+      <c r="I6" s="2"/>
+      <c r="J6" s="2">
         <v>0.40603051021903602</v>
       </c>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
     </row>
     <row r="9" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
     </row>
     <row r="11" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
     </row>
     <row r="12" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
     </row>
     <row r="13" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
     </row>
     <row r="14" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
@@ -623,20 +623,42 @@
     </row>
   </sheetData>
   <mergeCells count="62">
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="L5:M5"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="L6:M6"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D13:E13"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B4:C4"/>
@@ -649,42 +671,20 @@
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="L5:M5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="L6:M6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Function 4/evals.xlsx
+++ b/Function 4/evals.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prithvi\Desktop\Imperial Course\Capstone-Project\Function 4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A2BA1FA-5DB4-4B5A-8AAC-2B3C5F6AE17A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D82CAA35-4746-46F5-9CD3-E8018872464C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -89,10 +89,10 @@
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -382,259 +382,299 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="2" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3" t="s">
+      <c r="C2" s="2"/>
+      <c r="D2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3" t="s">
+      <c r="E2" s="2"/>
+      <c r="F2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3" t="s">
+      <c r="G2" s="2"/>
+      <c r="H2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3" t="s">
+      <c r="I2" s="2"/>
+      <c r="J2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3" t="s">
+      <c r="K2" s="2"/>
+      <c r="L2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M2" s="2"/>
+      <c r="M2" s="3"/>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B3" s="3">
+      <c r="B3" s="2">
         <v>1</v>
       </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="2">
+      <c r="C3" s="2"/>
+      <c r="D3" s="3">
         <v>0</v>
       </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2">
+      <c r="E3" s="3"/>
+      <c r="F3" s="3">
         <v>0</v>
       </c>
-      <c r="G3" s="2"/>
+      <c r="G3" s="3"/>
       <c r="H3" s="4">
         <v>1</v>
       </c>
       <c r="I3" s="4"/>
-      <c r="J3" s="2">
+      <c r="J3" s="3">
         <v>1</v>
       </c>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2">
+      <c r="K3" s="3"/>
+      <c r="L3" s="3">
         <v>-40.348489596712497</v>
       </c>
-      <c r="M3" s="2"/>
+      <c r="M3" s="3"/>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B4" s="3">
+      <c r="B4" s="2">
         <v>2</v>
       </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="2">
+      <c r="C4" s="2"/>
+      <c r="D4" s="3">
         <v>0.38188439101149502</v>
       </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2">
+      <c r="E4" s="3"/>
+      <c r="F4" s="3">
         <v>0.40048806048405</v>
       </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2">
+      <c r="G4" s="3"/>
+      <c r="H4" s="3">
         <v>0.37367797637949901</v>
       </c>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2">
+      <c r="I4" s="3"/>
+      <c r="J4" s="3">
         <v>0.468096950835934</v>
       </c>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2">
+      <c r="K4" s="3"/>
+      <c r="L4" s="3">
         <v>-1.20567449112958</v>
       </c>
-      <c r="M4" s="2"/>
+      <c r="M4" s="3"/>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B5" s="3">
+      <c r="B5" s="2">
         <v>3</v>
       </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="2">
+      <c r="C5" s="2"/>
+      <c r="D5" s="3">
         <v>0.47217455396691399</v>
       </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2">
+      <c r="E5" s="3"/>
+      <c r="F5" s="3">
         <v>0.45735404032243598</v>
       </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2">
+      <c r="G5" s="3"/>
+      <c r="H5" s="3">
         <v>0.21534414919209699</v>
       </c>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2">
+      <c r="I5" s="3"/>
+      <c r="J5" s="3">
         <v>0.422766391601334</v>
       </c>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2">
+      <c r="K5" s="3"/>
+      <c r="L5" s="3">
         <v>-3.7543251842156602</v>
       </c>
-      <c r="M5" s="2"/>
+      <c r="M5" s="3"/>
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B6" s="3">
+      <c r="B6" s="2">
         <v>4</v>
       </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="2">
+      <c r="C6" s="2"/>
+      <c r="D6" s="3">
         <v>0.41113387811130298</v>
       </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2">
+      <c r="E6" s="3"/>
+      <c r="F6" s="3">
         <v>0.481364478139513</v>
       </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2">
+      <c r="G6" s="3"/>
+      <c r="H6" s="3">
         <v>0.45430953159790799</v>
       </c>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2">
+      <c r="I6" s="3"/>
+      <c r="J6" s="3">
         <v>0.40603051021903602</v>
       </c>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3">
+        <v>-1.4025402736211301</v>
+      </c>
+      <c r="M6" s="3"/>
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
+      <c r="B7" s="3">
+        <v>5</v>
+      </c>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3">
+        <v>0.44970941830221201</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3">
+        <v>0.36413161747502698</v>
+      </c>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3">
+        <v>0.43564966660486099</v>
+      </c>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3">
+        <v>0.42411492476533702</v>
+      </c>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
     </row>
     <row r="9" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
     </row>
     <row r="11" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
     </row>
     <row r="12" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
     </row>
     <row r="13" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
     </row>
     <row r="14" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="62">
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
+  <mergeCells count="64">
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="L5:M5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="L6:M6"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="L7:M7"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D13:E13"/>
     <mergeCell ref="F4:G4"/>
     <mergeCell ref="F5:G5"/>
     <mergeCell ref="H9:I9"/>
@@ -647,44 +687,18 @@
     <mergeCell ref="H6:I6"/>
     <mergeCell ref="H7:I7"/>
     <mergeCell ref="H8:I8"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="L5:M5"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="L6:M6"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="J4:K4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Function 4/evals.xlsx
+++ b/Function 4/evals.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prithvi\Desktop\Imperial Course\Capstone-Project\Function 4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D82CAA35-4746-46F5-9CD3-E8018872464C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49C9C77E-D74C-4681-9D9E-D75DAA649FE5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -89,10 +89,10 @@
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -382,275 +382,307 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="2" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2" t="s">
+      <c r="C2" s="3"/>
+      <c r="D2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2" t="s">
+      <c r="E2" s="3"/>
+      <c r="F2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2" t="s">
+      <c r="G2" s="3"/>
+      <c r="H2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2" t="s">
+      <c r="I2" s="3"/>
+      <c r="J2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2" t="s">
+      <c r="K2" s="3"/>
+      <c r="L2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M2" s="3"/>
+      <c r="M2" s="2"/>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B3" s="2">
+      <c r="B3" s="3">
         <v>1</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="3">
+      <c r="C3" s="3"/>
+      <c r="D3" s="2">
         <v>0</v>
       </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3">
+      <c r="E3" s="2"/>
+      <c r="F3" s="2">
         <v>0</v>
       </c>
-      <c r="G3" s="3"/>
+      <c r="G3" s="2"/>
       <c r="H3" s="4">
         <v>1</v>
       </c>
       <c r="I3" s="4"/>
-      <c r="J3" s="3">
+      <c r="J3" s="2">
         <v>1</v>
       </c>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3">
+      <c r="K3" s="2"/>
+      <c r="L3" s="2">
         <v>-40.348489596712497</v>
       </c>
-      <c r="M3" s="3"/>
+      <c r="M3" s="2"/>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B4" s="2">
+      <c r="B4" s="3">
         <v>2</v>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="3">
+      <c r="C4" s="3"/>
+      <c r="D4" s="2">
         <v>0.38188439101149502</v>
       </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3">
+      <c r="E4" s="2"/>
+      <c r="F4" s="2">
         <v>0.40048806048405</v>
       </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3">
+      <c r="G4" s="2"/>
+      <c r="H4" s="2">
         <v>0.37367797637949901</v>
       </c>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3">
+      <c r="I4" s="2"/>
+      <c r="J4" s="2">
         <v>0.468096950835934</v>
       </c>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3">
+      <c r="K4" s="2"/>
+      <c r="L4" s="2">
         <v>-1.20567449112958</v>
       </c>
-      <c r="M4" s="3"/>
+      <c r="M4" s="2"/>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B5" s="2">
+      <c r="B5" s="3">
         <v>3</v>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="3">
+      <c r="C5" s="3"/>
+      <c r="D5" s="2">
         <v>0.47217455396691399</v>
       </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3">
+      <c r="E5" s="2"/>
+      <c r="F5" s="2">
         <v>0.45735404032243598</v>
       </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3">
+      <c r="G5" s="2"/>
+      <c r="H5" s="2">
         <v>0.21534414919209699</v>
       </c>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3">
+      <c r="I5" s="2"/>
+      <c r="J5" s="2">
         <v>0.422766391601334</v>
       </c>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3">
+      <c r="K5" s="2"/>
+      <c r="L5" s="2">
         <v>-3.7543251842156602</v>
       </c>
-      <c r="M5" s="3"/>
+      <c r="M5" s="2"/>
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B6" s="2">
+      <c r="B6" s="3">
         <v>4</v>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="3">
+      <c r="C6" s="3"/>
+      <c r="D6" s="2">
         <v>0.41113387811130298</v>
       </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3">
+      <c r="E6" s="2"/>
+      <c r="F6" s="2">
         <v>0.481364478139513</v>
       </c>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3">
+      <c r="G6" s="2"/>
+      <c r="H6" s="2">
         <v>0.45430953159790799</v>
       </c>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3">
+      <c r="I6" s="2"/>
+      <c r="J6" s="2">
         <v>0.40603051021903602</v>
       </c>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3">
+      <c r="K6" s="2"/>
+      <c r="L6" s="2">
         <v>-1.4025402736211301</v>
       </c>
-      <c r="M6" s="3"/>
+      <c r="M6" s="2"/>
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B7" s="3">
         <v>5</v>
       </c>
       <c r="C7" s="3"/>
-      <c r="D7" s="3">
+      <c r="D7" s="2">
         <v>0.44970941830221201</v>
       </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3">
+      <c r="E7" s="2"/>
+      <c r="F7" s="2">
         <v>0.36413161747502698</v>
       </c>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3">
+      <c r="G7" s="2"/>
+      <c r="H7" s="2">
         <v>0.43564966660486099</v>
       </c>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3">
+      <c r="I7" s="2"/>
+      <c r="J7" s="2">
         <v>0.42411492476533702</v>
       </c>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2">
+        <v>0.103552646669357</v>
+      </c>
+      <c r="M7" s="2"/>
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B8" s="3"/>
+      <c r="B8" s="3">
+        <v>6</v>
+      </c>
       <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
+      <c r="D8" s="2">
+        <v>0.43467017985664702</v>
+      </c>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2">
+        <v>0.31789642852327898</v>
+      </c>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2">
+        <v>0.467131532753985</v>
+      </c>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2">
+        <v>0.40586297125006798</v>
+      </c>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
     </row>
     <row r="9" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
     </row>
     <row r="11" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
     </row>
     <row r="12" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
     </row>
     <row r="13" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
     </row>
     <row r="14" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="64">
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="L5:M5"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="L6:M6"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="L7:M7"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="H12:I12"/>
+  <mergeCells count="66">
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D13:E13"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B4:C4"/>
@@ -663,42 +695,24 @@
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="L5:M5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="L6:M6"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="L7:M7"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="L8:M8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Function 4/evals.xlsx
+++ b/Function 4/evals.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prithvi\Desktop\Imperial Course\Capstone-Project\Function 4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49C9C77E-D74C-4681-9D9E-D75DAA649FE5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89A245B6-D4CA-48FA-BE94-A19CA9BBD612}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -558,22 +558,34 @@
         <v>0.40586297125006798</v>
       </c>
       <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
+      <c r="L8" s="2">
+        <v>-1.0992046232199499</v>
+      </c>
       <c r="M8" s="2"/>
     </row>
     <row r="9" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
+      <c r="B9" s="3">
+        <v>7</v>
+      </c>
+      <c r="C9" s="3"/>
+      <c r="D9" s="2">
+        <v>0.52718512498680903</v>
+      </c>
       <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
+      <c r="F9" s="2">
+        <v>0.38273093790317197</v>
+      </c>
       <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
+      <c r="H9" s="2">
+        <v>0.412058451995445</v>
+      </c>
       <c r="I9" s="2"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
+      <c r="J9" s="2">
+        <v>0.48229326777440601</v>
+      </c>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B10" s="2"/>
@@ -646,7 +658,7 @@
       <c r="M14" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="66">
+  <mergeCells count="68">
     <mergeCell ref="L2:M2"/>
     <mergeCell ref="L3:M3"/>
     <mergeCell ref="L4:M4"/>
@@ -713,6 +725,8 @@
     <mergeCell ref="L7:M7"/>
     <mergeCell ref="J8:K8"/>
     <mergeCell ref="L8:M8"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="J9:K9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Function 4/evals.xlsx
+++ b/Function 4/evals.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prithvi\Desktop\Imperial Course\Capstone-Project\Function 4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89A245B6-D4CA-48FA-BE94-A19CA9BBD612}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F906A9A4-7869-4992-B08F-0D25F3F20655}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -89,10 +89,10 @@
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -379,340 +379,298 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:M14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B2" s="3" t="s">
+    <row r="2" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3" t="s">
+      <c r="C2" s="2"/>
+      <c r="D2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3" t="s">
+      <c r="E2" s="2"/>
+      <c r="F2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3" t="s">
+      <c r="G2" s="2"/>
+      <c r="H2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3" t="s">
+      <c r="I2" s="2"/>
+      <c r="J2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3" t="s">
+      <c r="K2" s="2"/>
+      <c r="L2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M2" s="2"/>
-    </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B3" s="3">
+      <c r="M2" s="3"/>
+    </row>
+    <row r="3" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B3" s="2">
         <v>1</v>
       </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="2">
+      <c r="C3" s="2"/>
+      <c r="D3" s="3">
         <v>0</v>
       </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2">
+      <c r="E3" s="3"/>
+      <c r="F3" s="3">
         <v>0</v>
       </c>
-      <c r="G3" s="2"/>
+      <c r="G3" s="3"/>
       <c r="H3" s="4">
         <v>1</v>
       </c>
       <c r="I3" s="4"/>
-      <c r="J3" s="2">
+      <c r="J3" s="3">
         <v>1</v>
       </c>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2">
+      <c r="K3" s="3"/>
+      <c r="L3" s="3">
         <v>-40.348489596712497</v>
       </c>
-      <c r="M3" s="2"/>
-    </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B4" s="3">
+      <c r="M3" s="3"/>
+    </row>
+    <row r="4" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B4" s="2">
         <v>2</v>
       </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="2">
+      <c r="C4" s="2"/>
+      <c r="D4" s="3">
         <v>0.38188439101149502</v>
       </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2">
+      <c r="E4" s="3"/>
+      <c r="F4" s="3">
         <v>0.40048806048405</v>
       </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2">
+      <c r="G4" s="3"/>
+      <c r="H4" s="3">
         <v>0.37367797637949901</v>
       </c>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2">
+      <c r="I4" s="3"/>
+      <c r="J4" s="3">
         <v>0.468096950835934</v>
       </c>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2">
+      <c r="K4" s="3"/>
+      <c r="L4" s="3">
         <v>-1.20567449112958</v>
       </c>
-      <c r="M4" s="2"/>
-    </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B5" s="3">
+      <c r="M4" s="3"/>
+    </row>
+    <row r="5" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B5" s="2">
         <v>3</v>
       </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="2">
+      <c r="C5" s="2"/>
+      <c r="D5" s="3">
         <v>0.47217455396691399</v>
       </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2">
+      <c r="E5" s="3"/>
+      <c r="F5" s="3">
         <v>0.45735404032243598</v>
       </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2">
+      <c r="G5" s="3"/>
+      <c r="H5" s="3">
         <v>0.21534414919209699</v>
       </c>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2">
+      <c r="I5" s="3"/>
+      <c r="J5" s="3">
         <v>0.422766391601334</v>
       </c>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2">
+      <c r="K5" s="3"/>
+      <c r="L5" s="3">
         <v>-3.7543251842156602</v>
       </c>
-      <c r="M5" s="2"/>
-    </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B6" s="3">
+      <c r="M5" s="3"/>
+    </row>
+    <row r="6" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B6" s="2">
         <v>4</v>
       </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="2">
+      <c r="C6" s="2"/>
+      <c r="D6" s="3">
         <v>0.41113387811130298</v>
       </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2">
+      <c r="E6" s="3"/>
+      <c r="F6" s="3">
         <v>0.481364478139513</v>
       </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2">
+      <c r="G6" s="3"/>
+      <c r="H6" s="3">
         <v>0.45430953159790799</v>
       </c>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2">
+      <c r="I6" s="3"/>
+      <c r="J6" s="3">
         <v>0.40603051021903602</v>
       </c>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2">
+      <c r="K6" s="3"/>
+      <c r="L6" s="3">
         <v>-1.4025402736211301</v>
       </c>
-      <c r="M6" s="2"/>
-    </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B7" s="3">
+      <c r="M6" s="3"/>
+    </row>
+    <row r="7" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B7" s="2">
         <v>5</v>
       </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="2">
+      <c r="C7" s="2"/>
+      <c r="D7" s="3">
         <v>0.44970941830221201</v>
       </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2">
+      <c r="E7" s="3"/>
+      <c r="F7" s="3">
         <v>0.36413161747502698</v>
       </c>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2">
+      <c r="G7" s="3"/>
+      <c r="H7" s="3">
         <v>0.43564966660486099</v>
       </c>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2">
+      <c r="I7" s="3"/>
+      <c r="J7" s="3">
         <v>0.42411492476533702</v>
       </c>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2">
+      <c r="K7" s="3"/>
+      <c r="L7" s="3">
         <v>0.103552646669357</v>
       </c>
-      <c r="M7" s="2"/>
-    </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B8" s="3">
+      <c r="M7" s="3"/>
+    </row>
+    <row r="8" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B8" s="2">
         <v>6</v>
       </c>
-      <c r="C8" s="3"/>
-      <c r="D8" s="2">
+      <c r="C8" s="2"/>
+      <c r="D8" s="3">
         <v>0.43467017985664702</v>
       </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2">
+      <c r="E8" s="3"/>
+      <c r="F8" s="3">
         <v>0.31789642852327898</v>
       </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2">
+      <c r="G8" s="3"/>
+      <c r="H8" s="3">
         <v>0.467131532753985</v>
       </c>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2">
+      <c r="I8" s="3"/>
+      <c r="J8" s="3">
         <v>0.40586297125006798</v>
       </c>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2">
+      <c r="K8" s="3"/>
+      <c r="L8" s="3">
         <v>-1.0992046232199499</v>
       </c>
-      <c r="M8" s="2"/>
-    </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B9" s="3">
+      <c r="M8" s="3"/>
+    </row>
+    <row r="9" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B9" s="2">
         <v>7</v>
       </c>
-      <c r="C9" s="3"/>
-      <c r="D9" s="2">
+      <c r="C9" s="2"/>
+      <c r="D9" s="3">
         <v>0.52718512498680903</v>
       </c>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2">
+      <c r="E9" s="3"/>
+      <c r="F9" s="3">
         <v>0.38273093790317197</v>
       </c>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2">
+      <c r="G9" s="3"/>
+      <c r="H9" s="3">
         <v>0.412058451995445</v>
       </c>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2">
+      <c r="I9" s="3"/>
+      <c r="J9" s="3">
         <v>0.48229326777440601</v>
       </c>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
-    </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B10" s="2"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3">
+        <v>-2.6361882961982199</v>
+      </c>
+      <c r="M9" s="3"/>
+    </row>
+    <row r="10" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B10" s="2">
+        <v>8</v>
+      </c>
       <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
-    </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
+      <c r="D10" s="3">
+        <v>0.40473734876045298</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3">
+        <v>0.38515751021716499</v>
+      </c>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3">
+        <v>0.41094847654910999</v>
+      </c>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3">
+        <v>0.35761048397136602</v>
+      </c>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="3"/>
+    </row>
+    <row r="11" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
+    <row r="12" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
+    <row r="13" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
+    <row r="14" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="68">
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="H12:I12"/>
+  <mergeCells count="70">
     <mergeCell ref="F11:G11"/>
     <mergeCell ref="H11:I11"/>
     <mergeCell ref="H10:I10"/>
@@ -727,6 +685,62 @@
     <mergeCell ref="L8:M8"/>
     <mergeCell ref="L9:M9"/>
     <mergeCell ref="J9:K9"/>
+    <mergeCell ref="L10:M10"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="J4:K4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Function 4/evals.xlsx
+++ b/Function 4/evals.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prithvi\Desktop\Imperial Course\Capstone-Project\Function 4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F906A9A4-7869-4992-B08F-0D25F3F20655}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C859E2F-AF46-4461-855F-094A65BA9C1C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -89,10 +89,10 @@
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -379,298 +379,366 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:M14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B2" s="2" t="s">
+    <row r="2" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2" t="s">
+      <c r="C2" s="3"/>
+      <c r="D2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2" t="s">
+      <c r="E2" s="3"/>
+      <c r="F2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2" t="s">
+      <c r="G2" s="3"/>
+      <c r="H2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2" t="s">
+      <c r="I2" s="3"/>
+      <c r="J2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2" t="s">
+      <c r="K2" s="3"/>
+      <c r="L2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M2" s="3"/>
-    </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B3" s="2">
+      <c r="M2" s="2"/>
+    </row>
+    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B3" s="3">
         <v>1</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="3">
+      <c r="C3" s="3"/>
+      <c r="D3" s="2">
         <v>0</v>
       </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3">
+      <c r="E3" s="2"/>
+      <c r="F3" s="2">
         <v>0</v>
       </c>
-      <c r="G3" s="3"/>
+      <c r="G3" s="2"/>
       <c r="H3" s="4">
         <v>1</v>
       </c>
       <c r="I3" s="4"/>
-      <c r="J3" s="3">
+      <c r="J3" s="2">
         <v>1</v>
       </c>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3">
+      <c r="K3" s="2"/>
+      <c r="L3" s="2">
         <v>-40.348489596712497</v>
       </c>
-      <c r="M3" s="3"/>
-    </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B4" s="2">
+      <c r="M3" s="2"/>
+    </row>
+    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B4" s="3">
         <v>2</v>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="3">
+      <c r="C4" s="3"/>
+      <c r="D4" s="2">
         <v>0.38188439101149502</v>
       </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3">
+      <c r="E4" s="2"/>
+      <c r="F4" s="2">
         <v>0.40048806048405</v>
       </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3">
+      <c r="G4" s="2"/>
+      <c r="H4" s="2">
         <v>0.37367797637949901</v>
       </c>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3">
+      <c r="I4" s="2"/>
+      <c r="J4" s="2">
         <v>0.468096950835934</v>
       </c>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3">
+      <c r="K4" s="2"/>
+      <c r="L4" s="2">
         <v>-1.20567449112958</v>
       </c>
-      <c r="M4" s="3"/>
-    </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B5" s="2">
+      <c r="M4" s="2"/>
+    </row>
+    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B5" s="3">
         <v>3</v>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="3">
+      <c r="C5" s="3"/>
+      <c r="D5" s="2">
         <v>0.47217455396691399</v>
       </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3">
+      <c r="E5" s="2"/>
+      <c r="F5" s="2">
         <v>0.45735404032243598</v>
       </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3">
+      <c r="G5" s="2"/>
+      <c r="H5" s="2">
         <v>0.21534414919209699</v>
       </c>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3">
+      <c r="I5" s="2"/>
+      <c r="J5" s="2">
         <v>0.422766391601334</v>
       </c>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3">
+      <c r="K5" s="2"/>
+      <c r="L5" s="2">
         <v>-3.7543251842156602</v>
       </c>
-      <c r="M5" s="3"/>
-    </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B6" s="2">
+      <c r="M5" s="2"/>
+    </row>
+    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B6" s="3">
         <v>4</v>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="3">
+      <c r="C6" s="3"/>
+      <c r="D6" s="2">
         <v>0.41113387811130298</v>
       </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3">
+      <c r="E6" s="2"/>
+      <c r="F6" s="2">
         <v>0.481364478139513</v>
       </c>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3">
+      <c r="G6" s="2"/>
+      <c r="H6" s="2">
         <v>0.45430953159790799</v>
       </c>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3">
+      <c r="I6" s="2"/>
+      <c r="J6" s="2">
         <v>0.40603051021903602</v>
       </c>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3">
+      <c r="K6" s="2"/>
+      <c r="L6" s="2">
         <v>-1.4025402736211301</v>
       </c>
-      <c r="M6" s="3"/>
-    </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B7" s="2">
+      <c r="M6" s="2"/>
+    </row>
+    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B7" s="3">
         <v>5</v>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="3">
+      <c r="C7" s="3"/>
+      <c r="D7" s="2">
         <v>0.44970941830221201</v>
       </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3">
+      <c r="E7" s="2"/>
+      <c r="F7" s="2">
         <v>0.36413161747502698</v>
       </c>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3">
+      <c r="G7" s="2"/>
+      <c r="H7" s="2">
         <v>0.43564966660486099</v>
       </c>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3">
+      <c r="I7" s="2"/>
+      <c r="J7" s="2">
         <v>0.42411492476533702</v>
       </c>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3">
+      <c r="K7" s="2"/>
+      <c r="L7" s="2">
         <v>0.103552646669357</v>
       </c>
-      <c r="M7" s="3"/>
-    </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B8" s="2">
+      <c r="M7" s="2"/>
+    </row>
+    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B8" s="3">
         <v>6</v>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="3">
+      <c r="C8" s="3"/>
+      <c r="D8" s="2">
         <v>0.43467017985664702</v>
       </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3">
+      <c r="E8" s="2"/>
+      <c r="F8" s="2">
         <v>0.31789642852327898</v>
       </c>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3">
+      <c r="G8" s="2"/>
+      <c r="H8" s="2">
         <v>0.467131532753985</v>
       </c>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3">
+      <c r="I8" s="2"/>
+      <c r="J8" s="2">
         <v>0.40586297125006798</v>
       </c>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3">
+      <c r="K8" s="2"/>
+      <c r="L8" s="2">
         <v>-1.0992046232199499</v>
       </c>
-      <c r="M8" s="3"/>
-    </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B9" s="2">
+      <c r="M8" s="2"/>
+    </row>
+    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B9" s="3">
         <v>7</v>
       </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="3">
+      <c r="C9" s="3"/>
+      <c r="D9" s="2">
         <v>0.52718512498680903</v>
       </c>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3">
+      <c r="E9" s="2"/>
+      <c r="F9" s="2">
         <v>0.38273093790317197</v>
       </c>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3">
+      <c r="G9" s="2"/>
+      <c r="H9" s="2">
         <v>0.412058451995445</v>
       </c>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3">
+      <c r="I9" s="2"/>
+      <c r="J9" s="2">
         <v>0.48229326777440601</v>
       </c>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3">
+      <c r="K9" s="2"/>
+      <c r="L9" s="2">
         <v>-2.6361882961982199</v>
       </c>
-      <c r="M9" s="3"/>
-    </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B10" s="2">
+      <c r="M9" s="2"/>
+    </row>
+    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B10" s="3">
         <v>8</v>
       </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="3">
+      <c r="C10" s="3"/>
+      <c r="D10" s="2">
         <v>0.40473734876045298</v>
       </c>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3">
+      <c r="E10" s="2"/>
+      <c r="F10" s="2">
         <v>0.38515751021716499</v>
       </c>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3">
+      <c r="G10" s="2"/>
+      <c r="H10" s="2">
         <v>0.41094847654910999</v>
       </c>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3">
+      <c r="I10" s="2"/>
+      <c r="J10" s="2">
         <v>0.35761048397136602</v>
       </c>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
-    </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B11" s="3"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2">
+        <v>0.53388967765167195</v>
+      </c>
+      <c r="M10" s="2"/>
+    </row>
+    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B11" s="3">
+        <v>9</v>
+      </c>
       <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
-    </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
+      <c r="D11" s="2">
+        <v>0.48023402407643201</v>
+      </c>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2">
+        <v>0.38677933634586797</v>
+      </c>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2">
+        <v>0.41562159808548399</v>
+      </c>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2">
+        <v>0.42205969822815798</v>
+      </c>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+    </row>
+    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
+    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
+    <row r="14" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="70">
+  <mergeCells count="72">
+    <mergeCell ref="L11:M11"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="H12:I12"/>
     <mergeCell ref="F11:G11"/>
     <mergeCell ref="H11:I11"/>
     <mergeCell ref="H10:I10"/>
@@ -687,60 +755,6 @@
     <mergeCell ref="J9:K9"/>
     <mergeCell ref="L10:M10"/>
     <mergeCell ref="J10:K10"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="J4:K4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Function 4/evals.xlsx
+++ b/Function 4/evals.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prithvi\Desktop\Imperial Course\Capstone-Project\Function 4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C859E2F-AF46-4461-855F-094A65BA9C1C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{309D1791-8743-46C1-B71B-E6A5D8C37CAB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -379,9 +379,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:M14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
@@ -407,7 +407,7 @@
       </c>
       <c r="M2" s="2"/>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B3" s="3">
         <v>1</v>
       </c>
@@ -433,7 +433,7 @@
       </c>
       <c r="M3" s="2"/>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B4" s="3">
         <v>2</v>
       </c>
@@ -459,7 +459,7 @@
       </c>
       <c r="M4" s="2"/>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B5" s="3">
         <v>3</v>
       </c>
@@ -485,7 +485,7 @@
       </c>
       <c r="M5" s="2"/>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B6" s="3">
         <v>4</v>
       </c>
@@ -511,7 +511,7 @@
       </c>
       <c r="M6" s="2"/>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B7" s="3">
         <v>5</v>
       </c>
@@ -537,7 +537,7 @@
       </c>
       <c r="M7" s="2"/>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B8" s="3">
         <v>6</v>
       </c>
@@ -563,7 +563,7 @@
       </c>
       <c r="M8" s="2"/>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B9" s="3">
         <v>7</v>
       </c>
@@ -589,7 +589,7 @@
       </c>
       <c r="M9" s="2"/>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B10" s="3">
         <v>8</v>
       </c>
@@ -615,7 +615,7 @@
       </c>
       <c r="M10" s="2"/>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B11" s="3">
         <v>9</v>
       </c>
@@ -636,24 +636,36 @@
         <v>0.42205969822815798</v>
       </c>
       <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
+      <c r="L11" s="2">
+        <v>-0.93671503486464303</v>
+      </c>
       <c r="M11" s="2"/>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
+    <row r="12" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B12" s="3">
+        <v>10</v>
+      </c>
+      <c r="C12" s="3"/>
+      <c r="D12" s="2">
+        <v>0.43494815863115499</v>
+      </c>
       <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
+      <c r="F12" s="2">
+        <v>0.37896685948593101</v>
+      </c>
       <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
+      <c r="H12" s="2">
+        <v>0.46580325869240502</v>
+      </c>
       <c r="I12" s="2"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
-      <c r="M12" s="1"/>
-    </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="J12" s="2">
+        <v>0.52677190678006702</v>
+      </c>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+    </row>
+    <row r="13" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
@@ -667,7 +679,7 @@
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
@@ -682,63 +694,9 @@
       <c r="M14" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="72">
-    <mergeCell ref="L11:M11"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="H12:I12"/>
+  <mergeCells count="74">
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="J12:K12"/>
     <mergeCell ref="F11:G11"/>
     <mergeCell ref="H11:I11"/>
     <mergeCell ref="H10:I10"/>
@@ -755,6 +713,62 @@
     <mergeCell ref="J9:K9"/>
     <mergeCell ref="L10:M10"/>
     <mergeCell ref="J10:K10"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="L11:M11"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="J4:K4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Function 4/evals.xlsx
+++ b/Function 4/evals.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prithvi\Desktop\Imperial Course\Capstone-Project\Function 4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{309D1791-8743-46C1-B71B-E6A5D8C37CAB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8D00201-EA87-4FF7-9AE9-4090C05C68F6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -379,9 +379,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:M14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
@@ -407,7 +407,7 @@
       </c>
       <c r="M2" s="2"/>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B3" s="3">
         <v>1</v>
       </c>
@@ -433,7 +433,7 @@
       </c>
       <c r="M3" s="2"/>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B4" s="3">
         <v>2</v>
       </c>
@@ -459,7 +459,7 @@
       </c>
       <c r="M4" s="2"/>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B5" s="3">
         <v>3</v>
       </c>
@@ -485,7 +485,7 @@
       </c>
       <c r="M5" s="2"/>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B6" s="3">
         <v>4</v>
       </c>
@@ -511,7 +511,7 @@
       </c>
       <c r="M6" s="2"/>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B7" s="3">
         <v>5</v>
       </c>
@@ -537,7 +537,7 @@
       </c>
       <c r="M7" s="2"/>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B8" s="3">
         <v>6</v>
       </c>
@@ -563,7 +563,7 @@
       </c>
       <c r="M8" s="2"/>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B9" s="3">
         <v>7</v>
       </c>
@@ -589,7 +589,7 @@
       </c>
       <c r="M9" s="2"/>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B10" s="3">
         <v>8</v>
       </c>
@@ -615,7 +615,7 @@
       </c>
       <c r="M10" s="2"/>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B11" s="3">
         <v>9</v>
       </c>
@@ -641,7 +641,7 @@
       </c>
       <c r="M11" s="2"/>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B12" s="3">
         <v>10</v>
       </c>
@@ -662,24 +662,36 @@
         <v>0.52677190678006702</v>
       </c>
       <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
+      <c r="L12" s="2">
+        <v>-2.1642939438371198</v>
+      </c>
       <c r="M12" s="2"/>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
+    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B13" s="3">
+        <v>11</v>
+      </c>
+      <c r="C13" s="3"/>
+      <c r="D13" s="2">
+        <v>0.18198667053710799</v>
+      </c>
       <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
+      <c r="F13" s="2">
+        <v>0.38421805087367999</v>
+      </c>
       <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
+      <c r="H13" s="2">
+        <v>0.49936987407257899</v>
+      </c>
       <c r="I13" s="2"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="1"/>
-      <c r="M13" s="1"/>
-    </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="J13" s="2">
+        <v>0.45556448130438298</v>
+      </c>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+    </row>
+    <row r="14" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
@@ -694,31 +706,45 @@
       <c r="M14" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="74">
-    <mergeCell ref="L12:M12"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="L5:M5"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="L6:M6"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="L7:M7"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="L10:M10"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="H12:I12"/>
+  <mergeCells count="76">
+    <mergeCell ref="L13:M13"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D13:E13"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B4:C4"/>
@@ -731,44 +757,32 @@
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="L10:M10"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="L5:M5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="L6:M6"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="L7:M7"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="F10:G10"/>
     <mergeCell ref="L11:M11"/>
     <mergeCell ref="J11:K11"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="J4:K4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Function 4/evals.xlsx
+++ b/Function 4/evals.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prithvi\Desktop\Imperial Course\Capstone-Project\Function 4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8D00201-EA87-4FF7-9AE9-4090C05C68F6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D775E9CF-A81F-45CE-8464-A755C49D4BE1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -86,9 +86,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -382,333 +381,346 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="2" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3" t="s">
+      <c r="C2" s="2"/>
+      <c r="D2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3" t="s">
+      <c r="E2" s="2"/>
+      <c r="F2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3" t="s">
+      <c r="G2" s="2"/>
+      <c r="H2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3" t="s">
+      <c r="I2" s="2"/>
+      <c r="J2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3" t="s">
+      <c r="K2" s="2"/>
+      <c r="L2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M2" s="2"/>
+      <c r="M2" s="1"/>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B3" s="3">
+      <c r="B3" s="2">
         <v>1</v>
       </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="2">
+      <c r="C3" s="2"/>
+      <c r="D3" s="1">
         <v>0</v>
       </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2">
+      <c r="E3" s="1"/>
+      <c r="F3" s="1">
         <v>0</v>
       </c>
-      <c r="G3" s="2"/>
-      <c r="H3" s="4">
+      <c r="G3" s="1"/>
+      <c r="H3" s="3">
         <v>1</v>
       </c>
-      <c r="I3" s="4"/>
-      <c r="J3" s="2">
+      <c r="I3" s="3"/>
+      <c r="J3" s="1">
         <v>1</v>
       </c>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2">
+      <c r="K3" s="1"/>
+      <c r="L3" s="1">
         <v>-40.348489596712497</v>
       </c>
-      <c r="M3" s="2"/>
+      <c r="M3" s="1"/>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B4" s="3">
+      <c r="B4" s="2">
         <v>2</v>
       </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="2">
+      <c r="C4" s="2"/>
+      <c r="D4" s="1">
         <v>0.38188439101149502</v>
       </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2">
+      <c r="E4" s="1"/>
+      <c r="F4" s="1">
         <v>0.40048806048405</v>
       </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2">
+      <c r="G4" s="1"/>
+      <c r="H4" s="1">
         <v>0.37367797637949901</v>
       </c>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2">
+      <c r="I4" s="1"/>
+      <c r="J4" s="1">
         <v>0.468096950835934</v>
       </c>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2">
+      <c r="K4" s="1"/>
+      <c r="L4" s="1">
         <v>-1.20567449112958</v>
       </c>
-      <c r="M4" s="2"/>
+      <c r="M4" s="1"/>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B5" s="3">
+      <c r="B5" s="2">
         <v>3</v>
       </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="2">
+      <c r="C5" s="2"/>
+      <c r="D5" s="1">
         <v>0.47217455396691399</v>
       </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2">
+      <c r="E5" s="1"/>
+      <c r="F5" s="1">
         <v>0.45735404032243598</v>
       </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2">
+      <c r="G5" s="1"/>
+      <c r="H5" s="1">
         <v>0.21534414919209699</v>
       </c>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2">
+      <c r="I5" s="1"/>
+      <c r="J5" s="1">
         <v>0.422766391601334</v>
       </c>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2">
+      <c r="K5" s="1"/>
+      <c r="L5" s="1">
         <v>-3.7543251842156602</v>
       </c>
-      <c r="M5" s="2"/>
+      <c r="M5" s="1"/>
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B6" s="3">
+      <c r="B6" s="2">
         <v>4</v>
       </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="2">
+      <c r="C6" s="2"/>
+      <c r="D6" s="1">
         <v>0.41113387811130298</v>
       </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2">
+      <c r="E6" s="1"/>
+      <c r="F6" s="1">
         <v>0.481364478139513</v>
       </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2">
+      <c r="G6" s="1"/>
+      <c r="H6" s="1">
         <v>0.45430953159790799</v>
       </c>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2">
+      <c r="I6" s="1"/>
+      <c r="J6" s="1">
         <v>0.40603051021903602</v>
       </c>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2">
+      <c r="K6" s="1"/>
+      <c r="L6" s="1">
         <v>-1.4025402736211301</v>
       </c>
-      <c r="M6" s="2"/>
+      <c r="M6" s="1"/>
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B7" s="3">
+      <c r="B7" s="2">
         <v>5</v>
       </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="2">
+      <c r="C7" s="2"/>
+      <c r="D7" s="1">
         <v>0.44970941830221201</v>
       </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2">
+      <c r="E7" s="1"/>
+      <c r="F7" s="1">
         <v>0.36413161747502698</v>
       </c>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2">
+      <c r="G7" s="1"/>
+      <c r="H7" s="1">
         <v>0.43564966660486099</v>
       </c>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2">
+      <c r="I7" s="1"/>
+      <c r="J7" s="1">
         <v>0.42411492476533702</v>
       </c>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2">
+      <c r="K7" s="1"/>
+      <c r="L7" s="1">
         <v>0.103552646669357</v>
       </c>
-      <c r="M7" s="2"/>
+      <c r="M7" s="1"/>
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B8" s="3">
+      <c r="B8" s="2">
         <v>6</v>
       </c>
-      <c r="C8" s="3"/>
-      <c r="D8" s="2">
+      <c r="C8" s="2"/>
+      <c r="D8" s="1">
         <v>0.43467017985664702</v>
       </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2">
+      <c r="E8" s="1"/>
+      <c r="F8" s="1">
         <v>0.31789642852327898</v>
       </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2">
+      <c r="G8" s="1"/>
+      <c r="H8" s="1">
         <v>0.467131532753985</v>
       </c>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2">
+      <c r="I8" s="1"/>
+      <c r="J8" s="1">
         <v>0.40586297125006798</v>
       </c>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2">
+      <c r="K8" s="1"/>
+      <c r="L8" s="1">
         <v>-1.0992046232199499</v>
       </c>
-      <c r="M8" s="2"/>
+      <c r="M8" s="1"/>
     </row>
     <row r="9" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B9" s="3">
+      <c r="B9" s="2">
         <v>7</v>
       </c>
-      <c r="C9" s="3"/>
-      <c r="D9" s="2">
+      <c r="C9" s="2"/>
+      <c r="D9" s="1">
         <v>0.52718512498680903</v>
       </c>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2">
+      <c r="E9" s="1"/>
+      <c r="F9" s="1">
         <v>0.38273093790317197</v>
       </c>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2">
+      <c r="G9" s="1"/>
+      <c r="H9" s="1">
         <v>0.412058451995445</v>
       </c>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2">
+      <c r="I9" s="1"/>
+      <c r="J9" s="1">
         <v>0.48229326777440601</v>
       </c>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2">
+      <c r="K9" s="1"/>
+      <c r="L9" s="1">
         <v>-2.6361882961982199</v>
       </c>
-      <c r="M9" s="2"/>
+      <c r="M9" s="1"/>
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B10" s="3">
+      <c r="B10" s="2">
         <v>8</v>
       </c>
-      <c r="C10" s="3"/>
-      <c r="D10" s="2">
+      <c r="C10" s="2"/>
+      <c r="D10" s="1">
         <v>0.40473734876045298</v>
       </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2">
+      <c r="E10" s="1"/>
+      <c r="F10" s="1">
         <v>0.38515751021716499</v>
       </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2">
+      <c r="G10" s="1"/>
+      <c r="H10" s="1">
         <v>0.41094847654910999</v>
       </c>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2">
+      <c r="I10" s="1"/>
+      <c r="J10" s="1">
         <v>0.35761048397136602</v>
       </c>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2">
+      <c r="K10" s="1"/>
+      <c r="L10" s="1">
         <v>0.53388967765167195</v>
       </c>
-      <c r="M10" s="2"/>
+      <c r="M10" s="1"/>
     </row>
     <row r="11" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B11" s="3">
+      <c r="B11" s="2">
         <v>9</v>
       </c>
-      <c r="C11" s="3"/>
-      <c r="D11" s="2">
+      <c r="C11" s="2"/>
+      <c r="D11" s="1">
         <v>0.48023402407643201</v>
       </c>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2">
+      <c r="E11" s="1"/>
+      <c r="F11" s="1">
         <v>0.38677933634586797</v>
       </c>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2">
+      <c r="G11" s="1"/>
+      <c r="H11" s="1">
         <v>0.41562159808548399</v>
       </c>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2">
+      <c r="I11" s="1"/>
+      <c r="J11" s="1">
         <v>0.42205969822815798</v>
       </c>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2">
+      <c r="K11" s="1"/>
+      <c r="L11" s="1">
         <v>-0.93671503486464303</v>
       </c>
-      <c r="M11" s="2"/>
+      <c r="M11" s="1"/>
     </row>
     <row r="12" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B12" s="3">
+      <c r="B12" s="2">
         <v>10</v>
       </c>
-      <c r="C12" s="3"/>
-      <c r="D12" s="2">
+      <c r="C12" s="2"/>
+      <c r="D12" s="1">
         <v>0.43494815863115499</v>
       </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2">
+      <c r="E12" s="1"/>
+      <c r="F12" s="1">
         <v>0.37896685948593101</v>
       </c>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2">
+      <c r="G12" s="1"/>
+      <c r="H12" s="1">
         <v>0.46580325869240502</v>
       </c>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2">
+      <c r="I12" s="1"/>
+      <c r="J12" s="1">
         <v>0.52677190678006702</v>
       </c>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2">
+      <c r="K12" s="1"/>
+      <c r="L12" s="1">
         <v>-2.1642939438371198</v>
       </c>
-      <c r="M12" s="2"/>
+      <c r="M12" s="1"/>
     </row>
     <row r="13" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B13" s="3">
+      <c r="B13" s="2">
         <v>11</v>
       </c>
-      <c r="C13" s="3"/>
-      <c r="D13" s="2">
+      <c r="C13" s="2"/>
+      <c r="D13" s="1">
         <v>0.18198667053710799</v>
       </c>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2">
+      <c r="E13" s="1"/>
+      <c r="F13" s="1">
         <v>0.38421805087367999</v>
       </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2">
+      <c r="G13" s="1"/>
+      <c r="H13" s="1">
         <v>0.49936987407257899</v>
       </c>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2">
+      <c r="I13" s="1"/>
+      <c r="J13" s="1">
         <v>0.45556448130438298</v>
       </c>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1">
+        <v>-4.7077137725460698</v>
+      </c>
+      <c r="M13" s="1"/>
     </row>
     <row r="14" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B14" s="2"/>
+      <c r="B14" s="2">
+        <v>12</v>
+      </c>
       <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="1"/>
+      <c r="D14" s="1">
+        <v>0.41388196120224902</v>
+      </c>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1">
+        <v>0.35293074094171201</v>
+      </c>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1">
+        <v>0.45783928169698401</v>
+      </c>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1">
+        <v>0.44934741728213601</v>
+      </c>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="76">
-    <mergeCell ref="L13:M13"/>
-    <mergeCell ref="J13:K13"/>
+  <mergeCells count="78">
+    <mergeCell ref="L5:M5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="J14:K14"/>
     <mergeCell ref="L2:M2"/>
     <mergeCell ref="L3:M3"/>
     <mergeCell ref="L4:M4"/>
@@ -757,32 +769,33 @@
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B13:C13"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="L6:M6"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="L7:M7"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="L10:M10"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="L14:M14"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="L11:M11"/>
+    <mergeCell ref="J11:K11"/>
     <mergeCell ref="H13:I13"/>
     <mergeCell ref="H14:I14"/>
     <mergeCell ref="F13:G13"/>
     <mergeCell ref="F14:G14"/>
     <mergeCell ref="F12:G12"/>
     <mergeCell ref="H12:I12"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="L10:M10"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="L5:M5"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="L6:M6"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="L7:M7"/>
-    <mergeCell ref="L12:M12"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="L11:M11"/>
-    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="L13:M13"/>
+    <mergeCell ref="J13:K13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
